--- a/data/daily/2026-09/2026-09-20.xlsx
+++ b/data/daily/2026-09/2026-09-20.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,85 +1317,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1425,52 +1425,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,129 +1503,104 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2596,23 +2596,19 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16094</v>
+        <v>16096</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로 해소 및 활력 충전에 즉각적인 효과가 있음</t>
+          <t>우수한 피로 회복 효과 — 피곤할 때 복용하면 피로 회복에 즉각적인 도움을 줌</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 포장이 럭셔리하고 완성도가 높아 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>간편한 섭취 및 빠른 배송 — 먹기 편리하며 배송이 빠르게 처리됨</t>
-        </is>
-      </c>
+          <t>편리하고 고급스러운 형태 — 섭취가 간편하며 고급스러운 외관으로 선물용에 적합함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2655,21 +2651,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15424</v>
+        <v>15423</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간편한 올인원 제형 — 액상과 알약이 올인원으로 구성되어 손에 묻지 않고 섭취가 간편함</t>
+          <t>간편한 올인원 섭취 — 알약과 액상 앰플이 합쳐져 손에 묻히지 않고 간편히 복용 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 체력 및 컨디션 회복에 큰 도움이 됨</t>
+          <t>컨디션 개선 및 체력 보충 — 지치거나 피곤한 날 섭취 시 컨디션 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 선물용 패키지 구성과 포장이 고급스러움</t>
+          <t>고급스러운 패키지 구성 — 선물 포장 및 선물 패키지 구성이 세련되어 만족스러움</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2718,21 +2714,25 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 섭취 후 기력이 나고 덜 피곤한 느낌을 줌</t>
+          <t>체력 및 에너지 충전 — 섭취 시 피로감이 줄어들고 몸에 힘이 나는 효과를 느낌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>명절 선물용 케이스 — 케이스가 예쁘고 고급스러워 선물용으로 만족스러움</t>
+          <t>선물하기 좋은 케이스 디자인 — 명절 에디션 케이스와 고급스러운 디자인으로 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 수령 후 가격이 추가 할인되어 아쉬움</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>가격 변동 발생 — 구매 직후 제품 가격이 추가 하락하여 아쉬움</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>부담스러운 제품 가격 — 직접 구매하기에는 가격대가 만만치 않아 부담스러움</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -2773,20 +2773,24 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8709</v>
+        <v>8710</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>우수한 활력 충전 효과 — 섭취 후 피로감이 줄고 생기를 되찾는 데 효과적임</t>
+          <t>체감되는 에너지는 보충 — 피로감이 줄어들고 밤에 잠이 안 올 정도로 강력한 힘이 생김</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 섭취와 서비스 — 매일 간편하게 챙겨 먹기 좋으며 추가 서비스 증정 구성이 우수함</t>
+          <t>만족스러운 가성비 및 서비스 — 증정 서비스 구성이 알차고 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>소변 색상의 일시적 변화 — 섭취 후 하루 종일 소변 색이 진한 노란색으로 변함</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2832,20 +2836,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 효과 — 피로 해소와 컨디션 회복에 매우 효과적임</t>
+          <t>빠른 컨디션 회복 체감 — 피로가 쌓였을 때 복용하면 컨디션 회복에 큰 도움이 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>목넘김 편한 작은 알약 — 알약 크기가 크지 않아 쉽게 삼킬 수 있음</t>
+          <t>부담 없는 알약 크기 — 함께 들어있는 알약 크기가 크지 않아 넘기기 쉬움</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>고급스러운 포장 품질 — 포장이 깔끔하고 고급스러워 선물용으로 훌륭함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>정성스럽고 고급스러운 포장 — 포장이 깔끔하고 고급스러워 선물용으로 제격임</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>내용물 잔여로 인한 헹굼 필요 — 액상이 진해 용기에 남은 내용을 생수로 한 번 더 행궈 마셔야 함</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2887,22 +2895,26 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 효과 — 복용한 날과 안 먹은 날의 컨디션 차이가 체감됨</t>
+          <t>상쾌한 컨디션 회복 — 복용 후 피로 해소와 상쾌한 컨디션 유지에 효과적임</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>편리한 휴대 및 섭취 — 휴대하기 편하고 섭취 방법이 간단함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>뛰어난 휴대성과 편의성 — 챙겨 먹기 쉽고 휴대하기 편리한 올인원 제형임</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>깔끔한 명절 선물 패키지 — 쇼핑백 증정과 깔끔한 패키지 구성으로 선물용으로 만족스러움</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>배송 중 상자 파손 — 배송 과정에서 제품 박스가 찢어져서 도착함</t>
+          <t>명절 시즌 배송 지연 — 추석 연휴 직전 주문 시 배송이 다소 늦어짐</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2950,15 +2962,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>물 없이 먹는 간편함 — 젤리 구미 형태라 물 없이 편리하게 섭취 가능함</t>
+          <t>물 필요 없는 구미 제형 — 젤리 형태라 물 없이 어디서나 간단히 섭취 가능함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>귀여운 포장과 좋은 맛 — 포장이 귀엽고 맛이 좋아 매일 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>맛있고 부담 없는 맛 — 맛이 좋아 거부감 없이 매일 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>귀엽고 정성스러운 포장 — 귀여운 키캡 및 패키지 포장이 함께 구성되어 귀여움</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -3001,31 +3017,31 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>신뢰도 높은 브랜드 — 믿을 수 있는 브랜드이며 포장이 매우 고급스러움</t>
+          <t>새콤달콤한 오렌지 맛 — 새콤달콤한 오렌지 맛으로 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>새콤달콤 맛있는 복용법 — 새콤달콤한 오렌지 맛으로 간편하게 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>추가 증정 서비스 구성 — 1입 추가 증정 구성으로 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>고급스러운 포장과 증정 구성 — 패키지가 고급스럽고 추가 1입 증정 구성이 만족스러움</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>분말 뚜껑 개봉의 어려움 — 분말 뚜껑 부분을 강하게 눌러야 개봉됨</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3033,58 +3049,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
+          <t>'1입 추가 증정' "성별 맞춤 설계" 오쏘몰 바이탈 m/f 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7948462</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260918101845_2aa1c2f10c9e4652af1df550ad2cc225.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907084156_6695f5fa3b10400983a93ac3be43afb0.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>29568</v>
+        <v>770</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>효과적인 피로 해소 — 섭취 시 활력이 도르고 피로 회복에 우수함</t>
+          <t>지속되는 피로 개선 효과 — 꾸준히 복용 시 피로가 덜하고 활력이 유지됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>풍성한 사은품 구성 — 쇼핑백과 비타민젤리 등 사은품 혜택이 좋음</t>
+          <t>성별 맞춤 옵션 제공 — 성별(m/f)에 따라 영양소를 선택할 수 있어 유용함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>깔끔한 포장과 훌륭한 맛 — 맛이 좋고 종이 포장 및 구성이 깔끔함</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>정성스럽고 예쁜 선물 포장 — 선물 포장 및 디자인 구성이 매우 만족스러움</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>삼키기 힘든 알약 크기 — 기존 제품 대비 알약 크기가 커서 목 넘김이 힘듦</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3092,51 +3112,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>'1입 추가 증정' "성별 맞춤 설계" 오쏘몰 바이탈 m/f 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/7948462</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907084156_6695f5fa3b10400983a93ac3be43afb0.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260918101845_2aa1c2f10c9e4652af1df550ad2cc225.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>770</v>
+        <v>29571</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 제공 — 성별 맞춤 선택이 가능하며 영양 성분이 풍부함</t>
+          <t>빠른 활력 충전 효과 — 피로하고 지친 날 마시면 즉각적으로 에너지가 충전됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>오래 유지되는 효과 — 피로감이 줄고 반짝이는 기분이 오랫동안 유지됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>커다란 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 불편함</t>
-        </is>
-      </c>
+          <t>풍부한 추가 사은품 — 비타민젤리 등 알찬 사은품이 함께 제공되어 좋음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>선물용 종이가방 및 포장 — 쇼핑백과 고급스러운 종이 포장이 포함되어 선물에 적합함</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3178,22 +3198,22 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 보자기 포장 — 보자기와 틴케이스 등 정성스럽고 예쁜 포장을 제공함</t>
+          <t>화려하고 고급스러운 포장 — 보자기, 틴케이스, 핑크 박스 등 정성스럽고 고급스러운 포장임</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 맛 — 콜라겐 특유의 비린 맛이 없고 아주 맛있음</t>
+          <t>비리지 않고 맛있는 맛 — 콜라겐 특유의 비린 맛이 전혀 없고 맛있음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>부담스러운 가격 인상 — 제품 가격이 꾸준히 인상되어 자주 할인이 필요함</t>
+          <t>인상된 가격에 대한 부담 — 제품 품질은 만족스러우나 이전보다 가격이 올라 부담됨</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3241,18 +3261,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>훌륭한 소화 촉진 효과 — 식후 섭취 시 속이 편안해지고 소화가 잘 됨</t>
+          <t>속 편한 소화 촉진 — 식후 섭취 시 소화가 잘 되고 아침에 배변이 원활해짐</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>물 없는 섭취와 가성비 — 물 없이 먹을 수 있고 가격대 및 가성비가 훌륭함</t>
+          <t>물 없이 먹는 편의성 — 물 없이도 간편하게 털어 넣을 수 있어 복용이 편함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>기존 제품과의 맛 차이 — 기존 골드 카무트 제품과 맛의 차이가 느껴짐</t>
+          <t>기존 맛과의 체감 차이 — 기존 그레인골드 카무트 제품과 맛의 차이가 느껴짐</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3296,22 +3316,26 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>소화 및 배변 활동 개선 — 식후 소화 촉진 및 변비 완화에 큰 도움이 됨</t>
+          <t>소화 및 변비 개선 효과 — 식후 소화 촉진과 함께 변비 증상 개선에 도움을 줌</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>알찬 조건과 증정품 — 가격 조건이 좋고 추가 사은품이 풍부함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>방송 혜택 및 착한 가격 — 라이브방송 혜택을 통해 저렴하고 좋은 조건으로 구매 가능함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 포장 — 선물 포장이 고급스러워 부모님이나 아들 선물용으로 좋음</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>아쉬운 증정품 크기 — 증정품으로 제공된 단백질 칩의 크기가 다소 작음</t>
+          <t>아쉬운 증정품 용량 — 사은품으로 동봉된 단백질칩의 크기가 너무 작음</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3328,7 +3352,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3338,39 +3362,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>147</v>
+        <v>52</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>다양한 식단 구성 — 여러 가지 맛으로 구성되어 식단 관리에 용이함</t>
+          <t>부드럽고 다양한 맛 — 뻑뻑하지 않고 부드러우며 다채로운 맛으로 질리지 않음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>맛있고 뛰어난 가성비 — 닭가슴살 맛이 우수하며 보냉백 포함 가성비가 훌륭함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>우수한 패키지 가성비 — 저렴한 가격에 많은 수량의 닭가슴살을 구입할 수 있음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>전자레인지 조리의 간편함 — 전자레인지 조리가 가능해 다이어트 식단 관리가 간편함</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>배송 중 비닐 포장 터짐 — 포장이 헐렁하거나 터져 소스가 새어 나오는 경우가 있음</t>
+          <t>배송 중 해동 현상 — 배송되어 왔을 때 내용물이 전부 녹아서 도착함</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3387,7 +3415,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3397,39 +3425,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 뻑뻑하지 않고 부드러우며 자극적이지 않은 맛임</t>
+          <t>다양하고 풍부한 수량 — 다양한 맛으로 구성되어 식단용으로 골라 먹기 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 구성 — 다양한 종류로 구성되어 매일 먹어도 물리지 않음</t>
+          <t>실용적인 보냉백 증정 — 도시락을 싸 갖고 다니기 편한 보냉파우치를 사은품으로 제공함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 배송 시 제품이 완전히 녹아서 도착함</t>
+          <t>포장 터짐 및 소스 누수 — 진공 포장이 헐렁하거나 제품이 터져 내부 소스가 흘러넘침</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3477,18 +3505,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 편의성 — 말차 맛이 뛰어나고 간편하게 섭취 가능함</t>
+          <t>혜자스러운 에디션 구성 — 단백질바와 포토카드가 동봉되어 구성이 훌륭함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>만족스러운 굿즈 사은품 — 단백질바 및 멤버 포토카드 등의 구성 혜택이 좋음</t>
+          <t>부담 없는 베리말차 맛 — 말차를 잘 먹지 못하는 사람도 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>포토카드 고정 지급 — 포토카드가 랜덤 구성이 아닌 고정으로 지급됨</t>
+          <t>포토카드 고정 지급 방식 — 포토카드가 랜덤 지급이 아닌 고정 품목으로 제공됨</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3536,17 +3564,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 전혀 없음</t>
+          <t>비린 맛 없는 달콤함 — 단백질 음료 특유의 비리고 텁텁한 맛이 없고 우유처럼 맛있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>속 편한 영양 보충 — 마신 후 더부룩함이 없으며 식사 간 허기 채우기 좋음</t>
+          <t>속 편하고 부드러운 목넘김 — 마신 뒤 더부룩하지 않고 목넘김이 부드러움</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>슬림하고 편리한 휴대성 — 패키지가 슬림하여 가방에 넣어 휴대하기 용이함</t>
+          <t>든든한 포만감 형성 — 운동 후나 식사 사이 간식용으로 허기 채우기에 적합함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3595,18 +3623,18 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>고급스러운 용기 디자인 — 용기와 선물 포장이 고급스럽고 예쁨</t>
+          <t>예쁘고 고급스러운 용기 — 케이스와 병 디자인이 매우 고급스럽고 예쁨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>맛있는 앰플 형태 — 앰플 타입으로 거부감 없이 맛있게 섭취 가능함</t>
+          <t>맛있는 앰플 형태 — 비타민 음료처럼 맛있고 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>다소 진한 원액 농도 — 원액 맛이 다소 진하여 섭취 후 물을 마셔야 함</t>
+          <t>약간 진하고 감기약 같은 맛 — 농도가 진하며 비타민 음료와 감기약이 섞인 듯한 맛이 남</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3654,17 +3682,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>빠른 활력 증진 효과 — 고함량 아르기닌으로 피로 감소 및 지구력 증진에 효과적임</t>
+          <t>강력한 활력 및 체력 증진 — 초고함량 아르기닌 섭취로 운동 퍼포먼스와 컨디션 향상에 유용함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 상자 — 블랙/레드 디자인과 전용 쇼핑백으로 선물하기 좋음</t>
+          <t>휴대 및 복용의 간편함 — 1포씩 개별 포장되어 있어 가지고 다니며 복용하기 쉬움</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 — 1포씩 개별 포장되어 위생적이고 휴대가 간편함</t>
+          <t>고급스러운 선물 패키지 — 블랙/레드 상자와 쇼핑백, 추가 5포 증정으로 선물용에 최적화됨</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3674,7 +3702,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3682,51 +3710,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1534</v>
+        <v>11</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>알찬 이중 건강 케어 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 효율적임</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 두통과 속 뒤틀림 등 숙취가 현저히 감소함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>확실한 피로 감소 효과 — 아침 피로감이 감소하고 운동 시 컨디션 유지에 좋음</t>
+          <t>물 없이 짜먹는 스틱 제형 — 개별 액상 스틱 형태로 가방에 넣고 다니며 어디서나 먹기 편리함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>김종국 추천의 신뢰감 — 추천 세트 구성으로 신뢰도가 높고 쇼핑백이 포함됨</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>깔끔하고 고급스러운 패키지 — 보랏빛 디자인 포장이 깔끔하여 선물용 및 연말 모임 챙김용으로 좋음</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>쓴 한약 맛 잔여 — 맛이 한약 맛과 유사하여 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3881,12 +3913,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3970,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>종근당</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -3995,12 +4027,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>'1입 추가 증정' "성별 맞춤 설계" 오쏘몰 바이탈 m/f 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>'1입 추가 증정' "성별 맞춤 설계" 오쏘몰 바이탈 m/f 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
     </row>
@@ -4048,34 +4080,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16094</v>
+        <v>16096</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15424</v>
+        <v>15423</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3358</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8709</v>
+        <v>8710</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>788</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>6481</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29568</v>
+        <v>770</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>770</v>
+        <v>29571</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4086,71 +4118,72 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로 해소 및 활력 충전에 즉각적인 효과가 있음
-고급스러운 패키지 디자인 — 포장이 럭셔리하고 완성도가 높아 선물용으로 적합함
-간편한 섭취 및 빠른 배송 — 먹기 편리하며 배송이 빠르게 처리됨</t>
+          <t>우수한 피로 회복 효과 — 피곤할 때 복용하면 피로 회복에 즉각적인 도움을 줌
+편리하고 고급스러운 형태 — 섭취가 간편하며 고급스러운 외관으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 제형 — 액상과 알약이 올인원으로 구성되어 손에 묻지 않고 섭취가 간편함
-뛰어난 피로 회복 효과 — 체력 및 컨디션 회복에 큰 도움이 됨
-고급스러운 선물 포장 — 선물용 패키지 구성과 포장이 고급스러움</t>
+          <t>간편한 올인원 섭취 — 알약과 액상 앰플이 합쳐져 손에 묻히지 않고 간편히 복용 가능함
+컨디션 개선 및 체력 보충 — 지치거나 피곤한 날 섭취 시 컨디션 회복에 도움을 줌
+고급스러운 패키지 구성 — 선물 포장 및 선물 패키지 구성이 세련되어 만족스러움</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 섭취 후 기력이 나고 덜 피곤한 느낌을 줌
-명절 선물용 케이스 — 케이스가 예쁘고 고급스러워 선물용으로 만족스러움</t>
+          <t>체력 및 에너지 충전 — 섭취 시 피로감이 줄어들고 몸에 힘이 나는 효과를 느낌
+선물하기 좋은 케이스 디자인 — 명절 에디션 케이스와 고급스러운 디자인으로 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>우수한 활력 충전 효과 — 섭취 후 피로감이 줄고 생기를 되찾는 데 효과적임
-간편한 섭취와 서비스 — 매일 간편하게 챙겨 먹기 좋으며 추가 서비스 증정 구성이 우수함</t>
+          <t>체감되는 에너지는 보충 — 피로감이 줄어들고 밤에 잠이 안 올 정도로 강력한 힘이 생김
+만족스러운 가성비 및 서비스 — 증정 서비스 구성이 알차고 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 효과 — 피로 해소와 컨디션 회복에 매우 효과적임
-목넘김 편한 작은 알약 — 알약 크기가 크지 않아 쉽게 삼킬 수 있음
-고급스러운 포장 품질 — 포장이 깔끔하고 고급스러워 선물용으로 훌륭함</t>
+          <t>빠른 컨디션 회복 체감 — 피로가 쌓였을 때 복용하면 컨디션 회복에 큰 도움이 됨
+부담 없는 알약 크기 — 함께 들어있는 알약 크기가 크지 않아 넘기기 쉬움
+정성스럽고 고급스러운 포장 — 포장이 깔끔하고 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 효과 — 복용한 날과 안 먹은 날의 컨디션 차이가 체감됨
-편리한 휴대 및 섭취 — 휴대하기 편하고 섭취 방법이 간단함</t>
+          <t>상쾌한 컨디션 회복 — 복용 후 피로 해소와 상쾌한 컨디션 유지에 효과적임
+뛰어난 휴대성과 편의성 — 챙겨 먹기 쉽고 휴대하기 편리한 올인원 제형임
+깔끔한 명절 선물 패키지 — 쇼핑백 증정과 깔끔한 패키지 구성으로 선물용으로 만족스러움</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 먹는 간편함 — 젤리 구미 형태라 물 없이 편리하게 섭취 가능함
-귀여운 포장과 좋은 맛 — 포장이 귀엽고 맛이 좋아 매일 챙겨 먹기 좋음</t>
+          <t>물 필요 없는 구미 제형 — 젤리 형태라 물 없이 어디서나 간단히 섭취 가능함
+맛있고 부담 없는 맛 — 맛이 좋아 거부감 없이 매일 챙겨 먹기 편함
+귀엽고 정성스러운 포장 — 귀여운 키캡 및 패키지 포장이 함께 구성되어 귀여움</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>신뢰도 높은 브랜드 — 믿을 수 있는 브랜드이며 포장이 매우 고급스러움
-새콤달콤 맛있는 복용법 — 새콤달콤한 오렌지 맛으로 간편하게 마시기 좋음
-추가 증정 서비스 구성 — 1입 추가 증정 구성으로 만족도가 높음</t>
+          <t>새콤달콤한 오렌지 맛 — 새콤달콤한 오렌지 맛으로 맛있게 먹을 수 있음
+고급스러운 포장과 증정 구성 — 패키지가 고급스럽고 추가 1입 증정 구성이 만족스러움</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>효과적인 피로 해소 — 섭취 시 활력이 도르고 피로 회복에 우수함
-풍성한 사은품 구성 — 쇼핑백과 비타민젤리 등 사은품 혜택이 좋음
-깔끔한 포장과 훌륭한 맛 — 맛이 좋고 종이 포장 및 구성이 깔끔함</t>
+          <t>지속되는 피로 개선 효과 — 꾸준히 복용 시 피로가 덜하고 활력이 유지됨
+성별 맞춤 옵션 제공 — 성별(m/f)에 따라 영양소를 선택할 수 있어 유용함
+정성스럽고 예쁜 선물 포장 — 선물 포장 및 디자인 구성이 매우 만족스러움</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 제공 — 성별 맞춤 선택이 가능하며 영양 성분이 풍부함
-오래 유지되는 효과 — 피로감이 줄고 반짝이는 기분이 오랫동안 유지됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>빠른 활력 충전 효과 — 피로하고 지친 날 마시면 즉각적으로 에너지가 충전됨
+풍부한 추가 사은품 — 비타민젤리 등 알찬 사은품이 함께 제공되어 좋음
+선물용 종이가방 및 포장 — 쇼핑백과 고급스러운 종이 포장이 포함되어 선물에 적합함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4160,24 +4193,37 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 수령 후 가격이 추가 할인되어 아쉬움</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>가격 변동 발생 — 구매 직후 제품 가격이 추가 하락하여 아쉬움
+부담스러운 제품 가격 — 직접 구매하기에는 가격대가 만만치 않아 부담스러움</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>소변 색상의 일시적 변화 — 섭취 후 하루 종일 소변 색이 진한 노란색으로 변함</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>내용물 잔여로 인한 헹굼 필요 — 액상이 진해 용기에 남은 내용을 생수로 한 번 더 행궈 마셔야 함</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>배송 중 상자 파손 — 배송 과정에서 제품 박스가 찢어져서 도착함</t>
+          <t>명절 시즌 배송 지연 — 추석 연휴 직전 주문 시 배송이 다소 늦어짐</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>커다란 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 불편함</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>분말 뚜껑 개봉의 어려움 — 분말 뚜껑 부분을 강하게 눌러야 개봉됨</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>삼키기 힘든 알약 크기 — 기존 제품 대비 알약 크기가 커서 목 넘김이 힘듦</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4227,12 +4273,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>21,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4466,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4523,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
     </row>
@@ -4504,14 +4550,14 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
@@ -4534,7 +4580,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
     </row>
@@ -4582,19 +4628,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>880</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>147</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>52</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>93</v>
@@ -4609,7 +4655,7 @@
         <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1534</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4620,65 +4666,67 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 보자기 포장 — 보자기와 틴케이스 등 정성스럽고 예쁜 포장을 제공함
-비리지 않고 맛있는 맛 — 콜라겐 특유의 비린 맛이 없고 아주 맛있음</t>
+          <t>화려하고 고급스러운 포장 — 보자기, 틴케이스, 핑크 박스 등 정성스럽고 고급스러운 포장임
+비리지 않고 맛있는 맛 — 콜라겐 특유의 비린 맛이 전혀 없고 맛있음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>훌륭한 소화 촉진 효과 — 식후 섭취 시 속이 편안해지고 소화가 잘 됨
-물 없는 섭취와 가성비 — 물 없이 먹을 수 있고 가격대 및 가성비가 훌륭함</t>
+          <t>속 편한 소화 촉진 — 식후 섭취 시 소화가 잘 되고 아침에 배변이 원활해짐
+물 없이 먹는 편의성 — 물 없이도 간편하게 털어 넣을 수 있어 복용이 편함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>소화 및 배변 활동 개선 — 식후 소화 촉진 및 변비 완화에 큰 도움이 됨
-알찬 조건과 증정품 — 가격 조건이 좋고 추가 사은품이 풍부함</t>
+          <t>소화 및 변비 개선 효과 — 식후 소화 촉진과 함께 변비 증상 개선에 도움을 줌
+방송 혜택 및 착한 가격 — 라이브방송 혜택을 통해 저렴하고 좋은 조건으로 구매 가능함
+고급스러운 선물 포장 — 선물 포장이 고급스러워 부모님이나 아들 선물용으로 좋음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>다양한 식단 구성 — 여러 가지 맛으로 구성되어 식단 관리에 용이함
-맛있고 뛰어난 가성비 — 닭가슴살 맛이 우수하며 보냉백 포함 가성비가 훌륭함</t>
+          <t>부드럽고 다양한 맛 — 뻑뻑하지 않고 부드러우며 다채로운 맛으로 질리지 않음
+우수한 패키지 가성비 — 저렴한 가격에 많은 수량의 닭가슴살을 구입할 수 있음
+전자레인지 조리의 간편함 — 전자레인지 조리가 가능해 다이어트 식단 관리가 간편함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 뻑뻑하지 않고 부드러우며 자극적이지 않은 맛임
-질리지 않는 다양한 구성 — 다양한 종류로 구성되어 매일 먹어도 물리지 않음</t>
+          <t>다양하고 풍부한 수량 — 다양한 맛으로 구성되어 식단용으로 골라 먹기 좋음
+실용적인 보냉백 증정 — 도시락을 싸 갖고 다니기 편한 보냉파우치를 사은품으로 제공함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 편의성 — 말차 맛이 뛰어나고 간편하게 섭취 가능함
-만족스러운 굿즈 사은품 — 단백질바 및 멤버 포토카드 등의 구성 혜택이 좋음</t>
+          <t>혜자스러운 에디션 구성 — 단백질바와 포토카드가 동봉되어 구성이 훌륭함
+부담 없는 베리말차 맛 — 말차를 잘 먹지 못하는 사람도 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 전혀 없음
-속 편한 영양 보충 — 마신 후 더부룩함이 없으며 식사 간 허기 채우기 좋음
-슬림하고 편리한 휴대성 — 패키지가 슬림하여 가방에 넣어 휴대하기 용이함</t>
+          <t>비린 맛 없는 달콤함 — 단백질 음료 특유의 비리고 텁텁한 맛이 없고 우유처럼 맛있음
+속 편하고 부드러운 목넘김 — 마신 뒤 더부룩하지 않고 목넘김이 부드러움
+든든한 포만감 형성 — 운동 후나 식사 사이 간식용으로 허기 채우기에 적합함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 용기 디자인 — 용기와 선물 포장이 고급스럽고 예쁨
-맛있는 앰플 형태 — 앰플 타입으로 거부감 없이 맛있게 섭취 가능함</t>
+          <t>예쁘고 고급스러운 용기 — 케이스와 병 디자인이 매우 고급스럽고 예쁨
+맛있는 앰플 형태 — 비타민 음료처럼 맛있고 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>빠른 활력 증진 효과 — 고함량 아르기닌으로 피로 감소 및 지구력 증진에 효과적임
-고급스러운 선물용 상자 — 블랙/레드 디자인과 전용 쇼핑백으로 선물하기 좋음
-간편한 개별 포장 — 1포씩 개별 포장되어 위생적이고 휴대가 간편함</t>
+          <t>강력한 활력 및 체력 증진 — 초고함량 아르기닌 섭취로 운동 퍼포먼스와 컨디션 향상에 유용함
+휴대 및 복용의 간편함 — 1포씩 개별 포장되어 있어 가지고 다니며 복용하기 쉬움
+고급스러운 선물 패키지 — 블랙/레드 상자와 쇼핑백, 추가 5포 증정으로 선물용에 최적화됨</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>알찬 이중 건강 케어 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 효율적임
-확실한 피로 감소 효과 — 아침 피로감이 감소하고 운동 시 컨디션 유지에 좋음
-김종국 추천의 신뢰감 — 추천 세트 구성으로 신뢰도가 높고 쇼핑백이 포함됨</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 두통과 속 뒤틀림 등 숙취가 현저히 감소함
+물 없이 짜먹는 스틱 제형 — 개별 액상 스틱 형태로 가방에 넣고 다니며 어디서나 먹기 편리함
+깔끔하고 고급스러운 패키지 — 보랏빛 디자인 포장이 깔끔하여 선물용 및 연말 모임 챙김용으로 좋음</t>
         </is>
       </c>
     </row>
@@ -4690,42 +4738,46 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격 인상 — 제품 가격이 꾸준히 인상되어 자주 할인이 필요함</t>
+          <t>인상된 가격에 대한 부담 — 제품 품질은 만족스러우나 이전보다 가격이 올라 부담됨</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>기존 제품과의 맛 차이 — 기존 골드 카무트 제품과 맛의 차이가 느껴짐</t>
+          <t>기존 맛과의 체감 차이 — 기존 그레인골드 카무트 제품과 맛의 차이가 느껴짐</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 증정품 크기 — 증정품으로 제공된 단백질 칩의 크기가 다소 작음</t>
+          <t>아쉬운 증정품 용량 — 사은품으로 동봉된 단백질칩의 크기가 너무 작음</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 비닐 포장 터짐 — 포장이 헐렁하거나 터져 소스가 새어 나오는 경우가 있음</t>
+          <t>배송 중 해동 현상 — 배송되어 왔을 때 내용물이 전부 녹아서 도착함</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 배송 시 제품이 완전히 녹아서 도착함</t>
+          <t>포장 터짐 및 소스 누수 — 진공 포장이 헐렁하거나 제품이 터져 내부 소스가 흘러넘침</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>포토카드 고정 지급 — 포토카드가 랜덤 구성이 아닌 고정으로 지급됨</t>
+          <t>포토카드 고정 지급 방식 — 포토카드가 랜덤 지급이 아닌 고정 품목으로 제공됨</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>다소 진한 원액 농도 — 원액 맛이 다소 진하여 섭취 후 물을 마셔야 함</t>
+          <t>약간 진하고 감기약 같은 맛 — 농도가 진하며 비타민 음료와 감기약이 섞인 듯한 맛이 남</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>쓴 한약 맛 잔여 — 맛이 한약 맛과 유사하여 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4750,14 +4802,14 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
           <t>46,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
-        </is>
-      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>24,900원</t>
@@ -4780,7 +4832,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -4978,12 +5030,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>닥터블릿 위 건강 스페인 감초추출물 14정 14일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4993,30 +5045,26 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314465&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/SkTLQ0MeFl6Le3awtbuk286314465_00_00SkTLQ0MeFl6Le3awtbuk.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1498</v>
+        <v>22</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 가성비와 함량 — 가격 대비 글루타치온 함량이 훌륭함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>피부 톤 및 피로 개선 — 피로감이 감소하고 피부 톤이 밝아지는 느낌을 받음</t>
-        </is>
-      </c>
+          <t>위 불편감 완화 느낌 — 복용 후 위염 및 역류성 식도염 증상이 편안해지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -5025,7 +5073,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5033,12 +5081,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5048,28 +5096,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1090</v>
+        <v>6529</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 저렴한 가격 대비 만족도가 우수함</t>
+          <t>저렴한 가성비 영양제 — 부담 없는 저렴한 가격으로 매달 꾸준히 사 먹기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 복용 편의성 — 간단하고 편하게 복용하기 좋음</t>
+          <t>혈압 관리에 도움 — 꾸준히 복용 시 혈압 수치 케어에 도움을 느껴 만족함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -5080,7 +5128,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5088,12 +5136,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[여성건강] 종근당 데일리와이즈 리스펙타 유산균 6포 6일분</t>
+          <t>[보령약국 X Pantio] 2030 에너지 올인원 12포 12일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5103,43 +5151,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306212&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991013&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/LLM8nTqqNcWSJRgwJpaM032306212_00_01LLM8nTqqNcWSJRgwJpaM.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/qbG957X6MlxUkPfY6MmA033991013_00_00qbG957X6MlxUkPfY6MmA.png</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 맛 — 맛이 상큼하고 우수하여 먹기 편함</t>
+          <t>피로 개선 및 체력 회복 — 복용 후 몸의 피로감이 줄어들고 컨디션이 회복됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>저렴한 체험형 소용량 — 저렴한 가격으로 부담 없이 미리 체험하기 적합함</t>
+          <t>여행용 간편 포장 — 포장이 간편해 여행이나 외출 시 하나씩 챙겨가기 용이함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>다소 적은 포장 용량 — 6포 구성으로 전체적인 양이 다소 적음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5147,54 +5191,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘B 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618643&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/yaxFSMtpTnhrztKNOjGw601618643_00_00yaxFSMtpTnhrztKNOjGw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>568</v>
+        <v>86</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>마그네슘과 비타민B — 마그네슘과 비타민B를 함께 챙길 수 있어 피로 해소에 도움 됨</t>
+          <t>가성비 뛰어난 건강식품 — 다이소에서 저렴하게 구매 가능한 최고 가성비의 침향환임</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>풍부한 함량과 가성비 — 성분 함량이 우수하며 가성비가 높아 쟁여두기 좋음</t>
+          <t>활력 및 건강 증진 — 하루 한 알씩 섭취하며 몸이 건강해지고 활력이 생김</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>오래 남는 쓴 한약 맛 — 씹을수록 쓴 한약 맛이 강하게 나며 입안에 향이 오래 남음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5202,47 +5250,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>676</v>
+        <v>1271</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>휴대와 복용의 편의성 — 알약 크기가 적당하고 절단이 쉬워 휴대와 복용이 편함</t>
+          <t>상큼한 포카리 맛 — 물에 타 마시면 상큼한 포카리스웨트 맛이 나서 맛있음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>식후 혈당 관리 도움 — 식후 혈당이 신경 쓰일 때 간편하게 챙기기 좋음</t>
+          <t>여행용 휴대의 편리성 — 착한 가격에 스틱 형태로 되어 있어 여행 시 휴대하기 좋음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>강한 단맛의 호불호 — 단맛이 강해서 취향에 맞지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5257,58 +5309,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2175</v>
+        <v>419</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>위생적인 개별 포장 — 개별 포장 방식으로 휴대와 보관이 유용함</t>
+          <t>가성비 우수한 실속형 — 고물가 시대에 착한 가격과 넉넉한 양으로 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>에너지를 채우는 활력 — 활력 및 에너지 생성에 도움을 줌</t>
+          <t>초기 감기 및 목 관리 — 목감기 기운이 있거나 추울 때 따뜻하게 마시기 좋음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 제품 맛 — 제품 맛에 대한 만족도가 다소 떨어짐</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5316,12 +5364,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>[신혜선 PICK] 동국제약 프로폴리스＆아연 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5331,39 +5379,43 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/CJUce0AJqtqHn7R3ZFm1600000142_00_00CJUce0AJqtqHn7R3ZFm1.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/WQN2sdlFQlgUeYP1OzCA610911097_00_01WQN2sdlFQlgUeYP1OzCA.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>597</v>
+        <v>54</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>아이들이 좋아하는 맛 — 츄어블 형태로 맛이 좋아 어린이가 먹기 적합함</t>
+          <t>간편한 필름형 제형 — 필름 형태로 녹여 먹을 수 있어 들고 다니며 복용하기 용이함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>풍부한 영양과 가성비 — 가격이 착하고 여러 가지 영양소를 고루 갖춤</t>
+          <t>맛있고 쉬운 섭취 방법 — 맛이 좋아 챙겨 먹기 부담스럽지 않고 손쉽게 복용함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>약간 씁쓸하고 진한 맛 — 맛이 진하고 약간 쓴맛이 느껴짐</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5371,12 +5423,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5386,39 +5438,43 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1688</v>
+        <v>3602</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>부담 없는 뛰어난 가성비 — 가격이 저렴하고 부담 없이 구매 가능함</t>
+          <t>체중 감량 보조 효과 — 운동과 병행 섭취 시 체중이 빠지는 것이 몸으로 체감됨</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>기대되는 눈 피로 개선 — 눈 건강과 침침함 개선에 도움을 줌</t>
+          <t>원활한 배변 활동 — 복용 시 배변 활동이 원활해지는 효과가 탁월함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>대용량 구성의 부재 — 30일분 외에 50일/100일분 등 대용량 선택지가 없음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5426,7 +5482,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5441,39 +5497,43 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953530&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/j2jn8GpSpWpVPin1SKu2994953530_00_00j2jn8GpSpWpVPin1SKu2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>198</v>
+        <v>495</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>쓴맛 없는 달콤한 맛 — 쓴맛이 전혀 없어 맛있게 먹기 좋음</t>
+          <t>다음 날 피부 개선 체감 — 섭취 후 다음 날 피부가 매끈해진 느낌을 받음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>가격 대비 훌륭한 성분 — 저렴한 가격 대비 만족도가 우수함</t>
+          <t>한 포씩 쉬운 섭취 — 개별 스틱 포장으로 간단히 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>액체의 비린 맛으로 인한 불편 — 액상 특유의 비릿한 맛이 나서 삼키기가 다소 힘듦</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5481,7 +5541,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5496,34 +5556,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/CucIwXdPFflEtkJEtXZl613602126_00_01CucIwXdPFflEtkJEtXZl.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1305</v>
+        <v>1527</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>맛있는 구미 젤리 제형 — 맛과 식감이 훌륭한 젤리 형태로 아이들도 잘 먹음</t>
+          <t>맛있는 자몽맛 구미 — 영양제 맛 대신 맛있는 자몽 젤리를 먹는 느낌임</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>눈 건강 케어 효과 — 눈의 피로감을 줄이고 눈 건강을 지키는 데 유용함</t>
+          <t>물 없는 씹어먹는 편의성 — 물 없이 간편하게 씹어 먹을 수 있어 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>다소 단단한 젤리 식감 — 타 구미 제품에 비해 젤리 식감이 약간 단단한 편임</t>
+          <t>약간의 약 맛 느껴짐 — 젤리 맛 사이에 미세한 약 맛이 살짝 남아있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -5645,22 +5705,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5670,22 +5730,22 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -5697,42 +5757,42 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>판티오</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -5754,52 +5814,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>닥터블릿 위 건강 스페인 감초추출물 14정 14일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[여성건강] 종근당 데일리와이즈 리스펙타 유산균 6포 6일분</t>
+          <t>[보령약국 X Pantio] 2030 에너지 올인원 12포 12일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘B 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>[신혜선 PICK] 동국제약 프로폴리스＆아연 필름 12매 12일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5876,7 @@
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5825,7 +5885,7 @@
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
@@ -5834,7 +5894,7 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5847,34 +5907,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1498</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1090</v>
+        <v>6529</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>568</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>676</v>
+        <v>1271</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2175</v>
+        <v>419</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>597</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1688</v>
+        <v>3602</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>198</v>
+        <v>495</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1305</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5885,62 +5945,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비와 함량 — 가격 대비 글루타치온 함량이 훌륭함
-피부 톤 및 피로 개선 — 피로감이 감소하고 피부 톤이 밝아지는 느낌을 받음</t>
+          <t>위 불편감 완화 느낌 — 복용 후 위염 및 역류성 식도염 증상이 편안해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 저렴한 가격 대비 만족도가 우수함
-간편한 복용 편의성 — 간단하고 편하게 복용하기 좋음</t>
+          <t>저렴한 가성비 영양제 — 부담 없는 저렴한 가격으로 매달 꾸준히 사 먹기 좋음
+혈압 관리에 도움 — 꾸준히 복용 시 혈압 수치 케어에 도움을 느껴 만족함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 맛 — 맛이 상큼하고 우수하여 먹기 편함
-저렴한 체험형 소용량 — 저렴한 가격으로 부담 없이 미리 체험하기 적합함</t>
+          <t>피로 개선 및 체력 회복 — 복용 후 몸의 피로감이 줄어들고 컨디션이 회복됨
+여행용 간편 포장 — 포장이 간편해 여행이나 외출 시 하나씩 챙겨가기 용이함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>마그네슘과 비타민B — 마그네슘과 비타민B를 함께 챙길 수 있어 피로 해소에 도움 됨
-풍부한 함량과 가성비 — 성분 함량이 우수하며 가성비가 높아 쟁여두기 좋음</t>
+          <t>가성비 뛰어난 건강식품 — 다이소에서 저렴하게 구매 가능한 최고 가성비의 침향환임
+활력 및 건강 증진 — 하루 한 알씩 섭취하며 몸이 건강해지고 활력이 생김</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>휴대와 복용의 편의성 — 알약 크기가 적당하고 절단이 쉬워 휴대와 복용이 편함
-식후 혈당 관리 도움 — 식후 혈당이 신경 쓰일 때 간편하게 챙기기 좋음</t>
+          <t>상큼한 포카리 맛 — 물에 타 마시면 상큼한 포카리스웨트 맛이 나서 맛있음
+여행용 휴대의 편리성 — 착한 가격에 스틱 형태로 되어 있어 여행 시 휴대하기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>위생적인 개별 포장 — 개별 포장 방식으로 휴대와 보관이 유용함
-에너지를 채우는 활력 — 활력 및 에너지 생성에 도움을 줌</t>
+          <t>가성비 우수한 실속형 — 고물가 시대에 착한 가격과 넉넉한 양으로 가성비가 훌륭함
+초기 감기 및 목 관리 — 목감기 기운이 있거나 추울 때 따뜻하게 마시기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>아이들이 좋아하는 맛 — 츄어블 형태로 맛이 좋아 어린이가 먹기 적합함
-풍부한 영양과 가성비 — 가격이 착하고 여러 가지 영양소를 고루 갖춤</t>
+          <t>간편한 필름형 제형 — 필름 형태로 녹여 먹을 수 있어 들고 다니며 복용하기 용이함
+맛있고 쉬운 섭취 방법 — 맛이 좋아 챙겨 먹기 부담스럽지 않고 손쉽게 복용함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 뛰어난 가성비 — 가격이 저렴하고 부담 없이 구매 가능함
-기대되는 눈 피로 개선 — 눈 건강과 침침함 개선에 도움을 줌</t>
+          <t>체중 감량 보조 효과 — 운동과 병행 섭취 시 체중이 빠지는 것이 몸으로 체감됨
+원활한 배변 활동 — 복용 시 배변 활동이 원활해지는 효과가 탁월함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>쓴맛 없는 달콤한 맛 — 쓴맛이 전혀 없어 맛있게 먹기 좋음
-가격 대비 훌륭한 성분 — 저렴한 가격 대비 만족도가 우수함</t>
+          <t>다음 날 피부 개선 체감 — 섭취 후 다음 날 피부가 매끈해진 느낌을 받음
+한 포씩 쉬운 섭취 — 개별 스틱 포장으로 간단히 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 젤리 제형 — 맛과 식감이 훌륭한 젤리 형태로 아이들도 잘 먹음
-눈 건강 케어 효과 — 눈의 피로감을 줄이고 눈 건강을 지키는 데 유용함</t>
+          <t>맛있는 자몽맛 구미 — 영양제 맛 대신 맛있는 자몽 젤리를 먹는 느낌임
+물 없는 씹어먹는 편의성 — 물 없이 간편하게 씹어 먹을 수 있어 챙겨 먹기 용이함</t>
         </is>
       </c>
     </row>
@@ -5952,24 +6011,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>다소 적은 포장 용량 — 6포 구성으로 전체적인 양이 다소 적음</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 제품 맛 — 제품 맛에 대한 만족도가 다소 떨어짐</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>오래 남는 쓴 한약 맛 — 씹을수록 쓴 한약 맛이 강하게 나며 입안에 향이 오래 남음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>강한 단맛의 호불호 — 단맛이 강해서 취향에 맞지 않을 수 있음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>약간 씁쓸하고 진한 맛 — 맛이 진하고 약간 쓴맛이 느껴짐</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>대용량 구성의 부재 — 30일분 외에 50일/100일분 등 대용량 선택지가 없음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>액체의 비린 맛으로 인한 불편 — 액상 특유의 비릿한 맛이 나서 삼키기가 다소 힘듦</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>다소 단단한 젤리 식감 — 타 구미 제품에 비해 젤리 식감이 약간 단단한 편임</t>
+          <t>약간의 약 맛 느껴짐 — 젤리 맛 사이에 미세한 약 맛이 살짝 남아있음</t>
         </is>
       </c>
     </row>
@@ -5996,17 +6067,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -6205,7 +6276,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6213,35 +6284,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20264</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -6252,7 +6319,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6260,27 +6327,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6326,14 +6393,18 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8192</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>아침 빈속 1캡슐 섭취 — 아침 공복에 물과 함께 하루 1캡슐만 간편히 먹으면 됨</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>알찬 기획 및 증정품 — 더블기획 2달분 구성 및 포토카드 등 기획 혜택이 좋음</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -6342,7 +6413,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6350,33 +6421,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24464</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 케어 — 장 건강을 도와 몸 전체 면역력을 케어하는 데 필수적임</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>알찬 1+1 기획 구성 — 1+1 기획세트에 추가 증정품까지 더해져 쟁여두기 좋음</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -6385,7 +6468,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6393,50 +6476,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>375</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 질 건강과 장 건강을 한 번에 케어 가능함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>목넘김 편한 작은 캡슐 — 캡슐 사이즈가 작아 목넘김이 편함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>특별한 포켓몬 굿즈 — 포켓몬 에디션 카드케이스 증정 구성이 만족스러움</t>
-        </is>
-      </c>
+        <v>12605</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6444,7 +6515,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6452,42 +6523,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>확실한 피로 체감 감소 — 복용 후 아침에 몸이 가볍고 피로도가 다르게 느껴짐</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>고용량 비타민C 보충 — 100포 대용량으로 3000mg 고용량을 오랫동안 복용함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>충분한 수분 섭취 필수 — 결석 방지를 위해 하루에 물을 2L 이상 마셔주어야 함</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6495,27 +6578,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>9,200원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587419ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6530,7 +6613,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6538,35 +6621,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,200원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587419ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4875</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6577,7 +6656,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6585,42 +6664,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404813ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563462ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26764</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>원활한 배변 및 붓기 완화 — 복용 시 화장실을 잘 가며 붓기 해소 및 뱃살 관리에 유용함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>단기 체지방 관리 활용 — 과식 후나 단기 급찐급빠 관리용으로 효과가 미침</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 제품 알약 제형의 크기가 다소 커서 삼키기 불편함</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6628,37 +6723,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>세노비스</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28,030원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258054&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025805404ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>228</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>5957</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>빠른 숙면 및 수면 질 개선 — 자기 전 복용하면 빠르게 잠들고 아침에 개운하게 기상함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>맛있는 포도맛 젤리 — 마이구미처럼 맛있어 거부감 없이 매일 밤 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6775,52 +6878,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
         </is>
       </c>
     </row>
@@ -6832,52 +6935,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>세노비스</t>
+          <t>코자아</t>
         </is>
       </c>
     </row>
@@ -6889,52 +6992,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
     </row>
@@ -6944,25 +7047,23 @@
           <t>평점</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -6971,28 +7072,26 @@
           <t>리뷰수</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>20264</v>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="n">
-        <v>8192</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>24464</v>
+      </c>
       <c r="G7" s="3" t="n">
-        <v>375</v>
+        <v>12605</v>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
-        <v>4875</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="n">
+        <v>26764</v>
+      </c>
       <c r="L7" s="3" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>5957</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7000,20 +7099,39 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 질 건강과 장 건강을 한 번에 케어 가능함
-목넘김 편한 작은 캡슐 — 캡슐 사이즈가 작아 목넘김이 편함
-특별한 포켓몬 굿즈 — 포켓몬 에디션 카드케이스 증정 구성이 만족스러움</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>아침 빈속 1캡슐 섭취 — 아침 공복에 물과 함께 하루 1캡슐만 간편히 먹으면 됨
+알찬 기획 및 증정품 — 더블기획 2달분 구성 및 포토카드 등 기획 혜택이 좋음</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 케어 — 장 건강을 도와 몸 전체 면역력을 케어하는 데 필수적임
+알찬 1+1 기획 구성 — 1+1 기획세트에 추가 증정품까지 더해져 쟁여두기 좋음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 피로 체감 감소 — 복용 후 아침에 몸이 가볍고 피로도가 다르게 느껴짐
+고용량 비타민C 보충 — 100포 대용량으로 3000mg 고용량을 오랫동안 복용함</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>원활한 배변 및 붓기 완화 — 복용 시 화장실을 잘 가며 붓기 해소 및 뱃살 관리에 유용함
+단기 체지방 관리 활용 — 과식 후나 단기 급찐급빠 관리용으로 효과가 미침</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 숙면 및 수면 질 개선 — 자기 전 복용하면 빠르게 잠들고 아침에 개운하게 기상함
+맛있는 포도맛 젤리 — 마이구미처럼 맛있어 거부감 없이 매일 밤 챙겨 먹기 좋음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7026,10 +7144,18 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>충분한 수분 섭취 필수 — 결석 방지를 위해 하루에 물을 2L 이상 마셔주어야 함</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 제품 알약 제형의 크기가 다소 커서 삼키기 불편함</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7040,52 +7166,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>18,800원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>9,200원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>28,030원</t>
+          <t>32,900원</t>
         </is>
       </c>
     </row>
@@ -7215,19 +7341,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -7237,16 +7363,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -7259,47 +7385,47 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7309,19 +7435,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7334,29 +7460,29 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7365,7 +7491,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B9" t="n">
